--- a/Filtered/HCA_Florida_Northwest_Hospital.xlsx
+++ b/Filtered/HCA_Florida_Northwest_Hospital.xlsx
@@ -579,6 +579,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -636,6 +641,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -713,6 +723,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -770,6 +785,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -847,6 +867,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -904,6 +929,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -981,6 +1011,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1038,6 +1073,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1115,6 +1155,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1172,6 +1217,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1249,6 +1299,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1326,6 +1381,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1383,6 +1443,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1460,6 +1525,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1517,6 +1587,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1594,6 +1669,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1651,6 +1731,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1728,6 +1813,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1785,6 +1875,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1847,6 +1942,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1904,6 +2004,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1981,6 +2086,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2038,6 +2148,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2115,6 +2230,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2172,6 +2292,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2249,6 +2374,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2306,6 +2436,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2383,6 +2518,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2440,6 +2580,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2517,6 +2662,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2574,6 +2724,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2651,6 +2806,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2728,6 +2888,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2785,6 +2950,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2862,6 +3032,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2919,6 +3094,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2996,6 +3176,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3053,6 +3238,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3115,6 +3305,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3172,6 +3367,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3249,6 +3449,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3306,6 +3511,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3383,6 +3593,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3440,6 +3655,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3517,6 +3737,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3574,6 +3799,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3651,6 +3881,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3708,6 +3943,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3785,6 +4025,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3842,6 +4087,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3919,6 +4169,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3996,6 +4251,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4053,6 +4313,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4130,6 +4395,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4187,6 +4457,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4264,6 +4539,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4321,6 +4601,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4398,6 +4683,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4455,6 +4745,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4532,6 +4827,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4589,6 +4889,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4666,6 +4971,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4723,6 +5033,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4800,6 +5115,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4857,6 +5177,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4934,6 +5259,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4991,6 +5321,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5068,6 +5403,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5125,6 +5465,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5202,6 +5547,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5259,6 +5609,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5336,6 +5691,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5393,6 +5753,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5470,6 +5835,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5547,6 +5917,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5604,6 +5979,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5681,6 +6061,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5738,6 +6123,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5800,6 +6190,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5857,6 +6252,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5934,6 +6334,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5991,6 +6396,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6068,6 +6478,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6125,6 +6540,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6202,6 +6622,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6259,6 +6684,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6336,6 +6766,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6393,6 +6828,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6470,6 +6910,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6527,6 +6972,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6604,6 +7054,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6661,6 +7116,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6738,6 +7198,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6795,6 +7260,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6872,6 +7342,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6929,6 +7404,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7006,6 +7486,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7063,6 +7548,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7125,6 +7615,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7182,6 +7677,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7259,6 +7759,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7316,6 +7821,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7393,6 +7903,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7450,6 +7965,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7527,6 +8047,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7584,6 +8109,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7661,6 +8191,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7718,6 +8253,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7795,6 +8335,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7852,6 +8397,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7929,6 +8479,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7986,6 +8541,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8063,6 +8623,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8120,6 +8685,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8197,6 +8767,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8254,6 +8829,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8331,6 +8911,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8388,6 +8973,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8465,6 +9055,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8522,6 +9117,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8599,6 +9199,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8676,6 +9281,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8733,6 +9343,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8810,6 +9425,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M125" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8887,6 +9507,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M126" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8944,6 +9569,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9021,6 +9651,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M128" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9078,6 +9713,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9155,6 +9795,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9232,6 +9877,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M131" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9289,6 +9939,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M132" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9366,6 +10021,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M133" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9423,6 +10083,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M134" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9500,6 +10165,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M135" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9577,6 +10247,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9634,6 +10309,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9711,6 +10391,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9768,6 +10453,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9845,6 +10535,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9902,6 +10597,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9979,6 +10679,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10036,6 +10741,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10098,6 +10808,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10155,6 +10870,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10217,6 +10937,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10279,6 +11004,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10336,6 +11066,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10413,6 +11148,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10470,6 +11210,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10547,6 +11292,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M151" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10604,6 +11354,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10681,6 +11436,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M153" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10738,6 +11498,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M154" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10815,6 +11580,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M155" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10872,6 +11642,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10949,6 +11724,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11006,6 +11786,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11083,6 +11868,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11140,6 +11930,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11217,6 +12012,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11274,6 +12074,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M162" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11351,6 +12156,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11408,6 +12218,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11485,6 +12300,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M165" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11542,6 +12362,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11619,6 +12444,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11676,6 +12506,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11753,6 +12588,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M169" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11810,6 +12650,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11887,6 +12732,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M171" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11944,6 +12794,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12021,6 +12876,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12078,6 +12938,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M174" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12155,6 +13020,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12232,6 +13102,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12289,6 +13164,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12351,6 +13231,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12408,6 +13293,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12485,6 +13375,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12542,6 +13437,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12619,6 +13519,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12676,6 +13581,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12753,6 +13663,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12810,6 +13725,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12887,6 +13807,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12944,6 +13869,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13021,6 +13951,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13078,6 +14013,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M189" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13155,6 +14095,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13212,6 +14157,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13289,6 +14239,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13346,6 +14301,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13423,6 +14383,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13480,6 +14445,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13557,6 +14527,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13614,6 +14589,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13691,6 +14671,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13748,6 +14733,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13825,6 +14815,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13882,6 +14877,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13959,6 +14959,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M202" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14016,6 +15021,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M203" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14093,6 +15103,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M204" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14150,6 +15165,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M205" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14227,6 +15247,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14284,6 +15309,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14361,6 +15391,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M208" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14418,6 +15453,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M209" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14495,6 +15535,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M210" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14552,6 +15597,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14629,6 +15679,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M212" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14686,6 +15741,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M213" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14763,6 +15823,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M214" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14820,6 +15885,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14897,6 +15967,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M216" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14954,6 +16029,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15031,6 +16111,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M218" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15088,6 +16173,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M219" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15165,6 +16255,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M220" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15222,6 +16317,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15299,6 +16399,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M222" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15356,6 +16461,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M223" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15433,6 +16543,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M224" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15490,6 +16605,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15567,6 +16687,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M226" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15624,6 +16749,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M227" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15701,6 +16831,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M228" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15758,6 +16893,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M229" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15835,6 +16975,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M230" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15892,6 +17037,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M231" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15969,6 +17119,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16026,6 +17181,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16088,6 +17248,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16145,6 +17310,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16222,6 +17392,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16279,6 +17454,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16356,6 +17536,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16413,6 +17598,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16490,6 +17680,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16547,6 +17742,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16624,6 +17824,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16681,6 +17886,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16758,6 +17968,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16835,6 +18050,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16892,6 +18112,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16969,6 +18194,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17026,6 +18256,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17103,6 +18338,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17160,6 +18400,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17237,6 +18482,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17294,6 +18544,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17371,6 +18626,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M253" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17428,6 +18688,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17505,6 +18770,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17562,6 +18832,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M256" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17639,6 +18914,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17696,6 +18976,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17773,6 +19058,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17830,6 +19120,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17907,6 +19202,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17964,6 +19264,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M262" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18041,6 +19346,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18098,6 +19408,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18175,6 +19490,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18232,6 +19552,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18309,6 +19634,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18366,6 +19696,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18443,6 +19778,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M269" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18500,6 +19840,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18577,6 +19922,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18634,6 +19984,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18711,6 +20066,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18768,6 +20128,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18845,6 +20210,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18902,6 +20272,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18979,6 +20354,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19036,6 +20416,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19113,6 +20498,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19170,6 +20560,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19247,6 +20642,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19304,6 +20704,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19381,6 +20786,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19438,6 +20848,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19515,6 +20930,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19572,6 +20992,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19649,6 +21074,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M287" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19706,6 +21136,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19783,6 +21218,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19860,6 +21300,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19917,6 +21362,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M291" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19994,6 +21444,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20051,6 +21506,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20128,6 +21588,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20185,6 +21650,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20262,6 +21732,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M296" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20319,6 +21794,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20396,6 +21876,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20453,6 +21938,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M299" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20530,6 +22020,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M300" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20607,6 +22102,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20664,6 +22164,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M302" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20741,6 +22246,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20798,6 +22308,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20875,6 +22390,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20952,6 +22472,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21009,6 +22534,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M307" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21086,6 +22616,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M308" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21143,6 +22678,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21220,6 +22760,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M310" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21277,6 +22822,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M311" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21354,6 +22904,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21411,6 +22966,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M313" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21488,6 +23048,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21545,6 +23110,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M315" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21622,6 +23192,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M316" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21679,6 +23254,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M317" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21756,6 +23336,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M318" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21813,6 +23398,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M319" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21875,6 +23465,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21932,6 +23527,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M321" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22009,6 +23609,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22066,6 +23671,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M323" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22143,6 +23753,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22200,6 +23815,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M325" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22277,6 +23897,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22334,6 +23959,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22396,6 +24026,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M328" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22453,6 +24088,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22530,6 +24170,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22587,6 +24232,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22664,6 +24314,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22721,6 +24376,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M333" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22798,6 +24458,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22855,6 +24520,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22932,6 +24602,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22989,6 +24664,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23066,6 +24746,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23123,6 +24808,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23200,6 +24890,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23257,6 +24952,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23334,6 +25034,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23391,6 +25096,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23468,6 +25178,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23525,6 +25240,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23587,6 +25307,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23644,6 +25369,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23721,6 +25451,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23778,6 +25513,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23855,6 +25595,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23912,6 +25657,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23989,6 +25739,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24046,6 +25801,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24123,6 +25883,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24180,6 +25945,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24257,6 +26027,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24314,6 +26089,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24391,6 +26171,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24448,6 +26233,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24525,6 +26315,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24582,6 +26377,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24659,6 +26459,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24716,6 +26521,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24793,6 +26603,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24850,6 +26665,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24927,6 +26747,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24984,6 +26809,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25061,6 +26891,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M368" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25118,6 +26953,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25195,6 +27035,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25252,6 +27097,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25329,6 +27179,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M372" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25386,6 +27241,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25463,6 +27323,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M374" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25520,6 +27385,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25582,6 +27452,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M376" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25644,6 +27519,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M377" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25706,6 +27586,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M378" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25763,6 +27648,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25840,6 +27730,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25897,6 +27792,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25959,6 +27859,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26021,6 +27926,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26083,6 +27993,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26145,6 +28060,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26207,6 +28127,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26264,6 +28189,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26341,6 +28271,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26398,6 +28333,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26475,6 +28415,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26532,6 +28477,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26609,6 +28559,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26666,6 +28621,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26743,6 +28703,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26800,6 +28765,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26862,6 +28832,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26919,6 +28894,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26981,6 +28961,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27043,6 +29028,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27100,6 +29090,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27162,6 +29157,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27224,6 +29224,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27286,6 +29291,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27343,6 +29353,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27420,6 +29435,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27477,6 +29497,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27539,6 +29564,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27601,6 +29631,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27663,6 +29698,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27720,6 +29760,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27797,6 +29842,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27854,6 +29904,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27916,6 +29971,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27973,6 +30033,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28050,6 +30115,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28107,6 +30177,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28169,6 +30244,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28231,6 +30311,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28293,6 +30378,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28350,6 +30440,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M420" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28427,6 +30522,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28484,6 +30584,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28561,6 +30666,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M423" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28618,6 +30728,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28680,6 +30795,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28742,6 +30862,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28799,6 +30924,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M427" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28861,6 +30991,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M428" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28923,6 +31058,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M429" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28985,6 +31125,11 @@
           <t>COCNW</t>
         </is>
       </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M430" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29040,6 +31185,11 @@
       <c r="K431" t="inlineStr">
         <is>
           <t>COCNW</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
